--- a/data/trans_orig/Q5402-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2007</t>
+          <t>Población según si son capaces de prepararse la comida en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5875</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47015</t>
+          <t>47776</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75824</t>
+          <t>75004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86721</t>
+          <t>86124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48931</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>62788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53793</t>
+          <t>54515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>65762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87754</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24025</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19279</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,47 +2229,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2981</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13004</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>7,41%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>6356</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2279</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>12278</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23451</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45724</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206250</t>
+          <t>205865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228296</t>
+          <t>227780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72144</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82505</t>
+          <t>82426</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>283205</t>
+          <t>282966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>308641</t>
+          <t>308586</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22648</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66344</t>
+          <t>66514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84335</t>
+          <t>83401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111877</t>
+          <t>111470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131459</t>
+          <t>131565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32906</t>
+          <t>33579</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34266</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38838</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>360534</t>
+          <t>360268</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387542</t>
+          <t>387413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>363255</t>
+          <t>362709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>390740</t>
+          <t>390769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48510</t>
+          <t>49598</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79157</t>
+          <t>81702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35240</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>61063</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62298</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77439</t>
+          <t>80262</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116751</t>
+          <t>116697</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>414073</t>
+          <t>410529</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>443316</t>
+          <t>442383</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>572581</t>
+          <t>571453</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>608600</t>
+          <t>607620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>995780</t>
+          <t>991243</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1043068</t>
+          <t>1039556</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2012</t>
+          <t>Población según si son capaces de prepararse la comida en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41863</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>51984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65238</t>
+          <t>65948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>45621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>57635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57997</t>
+          <t>57952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72946</t>
+          <t>72861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>85980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104836</t>
+          <t>104465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39571</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>129749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152550</t>
+          <t>151755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43974</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45891</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57480</t>
+          <t>56839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154496</t>
+          <t>155083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182953</t>
+          <t>183876</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53221</t>
+          <t>52829</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>199185</t>
+          <t>198709</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230427</t>
+          <t>232050</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39523</t>
+          <t>39155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28672</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53431</t>
+          <t>54979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>32379</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,47 +6146,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>32055</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>21897</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>44518</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>32055</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>21377</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>43106</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70641</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87881</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124848</t>
+          <t>126412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149604</t>
+          <t>150973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203764</t>
+          <t>202538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>233060</t>
+          <t>232621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52884</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51386</t>
+          <t>52124</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22462</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46281</t>
+          <t>45756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45393</t>
+          <t>45836</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>305151</t>
+          <t>306924</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336631</t>
+          <t>338976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>308721</t>
+          <t>308572</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>340339</t>
+          <t>340039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>41497</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>59814</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>93715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>110039</t>
+          <t>108985</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>153983</t>
+          <t>155404</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83806</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58796</t>
+          <t>60676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93501</t>
+          <t>94315</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118687</t>
+          <t>119141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>167067</t>
+          <t>167895</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>416624</t>
+          <t>417477</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>458060</t>
+          <t>459168</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>567463</t>
+          <t>566623</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>614276</t>
+          <t>611264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>997839</t>
+          <t>995118</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1058465</t>
+          <t>1057656</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2016</t>
+          <t>Población según si son capaces de prepararse la comida en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,62 +7620,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4368</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60634</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67763</t>
+          <t>67792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35601</t>
+          <t>35636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88755</t>
+          <t>89519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102012</t>
+          <t>101979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,62 +8076,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>40181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>49865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>55555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66540</t>
+          <t>66673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>101192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114208</t>
+          <t>113869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30535</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41701</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135553</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153102</t>
+          <t>153679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>24660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>33093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163390</t>
+          <t>164472</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>182881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75113</t>
+          <t>73764</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91565</t>
+          <t>91259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244962</t>
+          <t>246704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270531</t>
+          <t>270610</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29092</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28260</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29087</t>
+          <t>28275</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103736</t>
+          <t>104323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122546</t>
+          <t>122670</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120250</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140610</t>
+          <t>141114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230659</t>
+          <t>230229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>257613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>46475</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>46475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>332981</t>
+          <t>331222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>366752</t>
+          <t>367209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332981</t>
+          <t>331222</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366752</t>
+          <t>367209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68660</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67826</t>
+          <t>68022</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>105846</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61979</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53252</t>
+          <t>54490</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91658</t>
+          <t>93046</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>97549</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>144842</t>
+          <t>144469</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>491258</t>
+          <t>491916</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>522793</t>
+          <t>522488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>628093</t>
+          <t>629765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>672516</t>
+          <t>674597</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1128849</t>
+          <t>1125910</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1187741</t>
+          <t>1186473</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2023</t>
+          <t>Población según si son capaces de prepararse la comida en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96259</t>
+          <t>96942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>104234</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53375</t>
+          <t>53531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61984</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154061</t>
+          <t>153146</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164780</t>
+          <t>164820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>79462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88683</t>
+          <t>88986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44535</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120942</t>
+          <t>120599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131950</t>
+          <t>131753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81134</t>
+          <t>81204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92658</t>
+          <t>92381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39488</t>
+          <t>39578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>47388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123900</t>
+          <t>123146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137495</t>
+          <t>137394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18348</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>34193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55001</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>22731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29788</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171613</t>
+          <t>171070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>192396</t>
+          <t>191495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>275029</t>
+          <t>275055</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>323159</t>
+          <t>322675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>443543</t>
+          <t>443758</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>540685</t>
+          <t>538636</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>26019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>36960</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>33651</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51384</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61595</t>
+          <t>62520</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74431</t>
+          <t>74121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143415</t>
+          <t>143688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160661</t>
+          <t>160404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210333</t>
+          <t>211490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>231084</t>
+          <t>231849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46856</t>
+          <t>46335</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>29666</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>38679</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56599</t>
+          <t>56160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>38834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>56318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>225909</t>
+          <t>225077</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248295</t>
+          <t>248776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>227212</t>
+          <t>228002</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>250563</t>
+          <t>250378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58263</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97093</t>
+          <t>97518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81738</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>144383</t>
+          <t>144806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51532</t>
+          <t>51210</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>74011</t>
+          <t>74022</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55769</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132281</t>
+          <t>130441</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>112421</t>
+          <t>103775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192709</t>
+          <t>192023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>511846</t>
+          <t>510728</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>540909</t>
+          <t>540836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>793677</t>
+          <t>793715</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>930257</t>
+          <t>930011</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1322393</t>
+          <t>1323055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1456079</t>
+          <t>1476548</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5402-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>58048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75004</t>
+          <t>74719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86124</t>
+          <t>86058</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49026</t>
+          <t>49058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62788</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54515</t>
+          <t>54617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65762</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73806</t>
+          <t>75043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87539</t>
+          <t>87752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>205865</t>
+          <t>206392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227780</t>
+          <t>228141</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>71803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82426</t>
+          <t>82398</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282966</t>
+          <t>283693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>308586</t>
+          <t>308766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>23135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>40408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50689</t>
+          <t>50852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66514</t>
+          <t>66739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83401</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111470</t>
+          <t>112940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131565</t>
+          <t>131568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38301</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>360268</t>
+          <t>359871</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387413</t>
+          <t>387561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>362709</t>
+          <t>362876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>390769</t>
+          <t>390650</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>36334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49598</t>
+          <t>46502</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81702</t>
+          <t>77921</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>62425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80262</t>
+          <t>78430</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116697</t>
+          <t>116435</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>410529</t>
+          <t>412509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>442383</t>
+          <t>442116</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>571453</t>
+          <t>572975</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>607620</t>
+          <t>608287</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>991243</t>
+          <t>993902</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1039556</t>
+          <t>1041227</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51984</t>
+          <t>52598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65948</t>
+          <t>65296</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>44414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57635</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57952</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>73035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27649</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85980</t>
+          <t>85641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104465</t>
+          <t>104981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39710</t>
+          <t>39421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50487</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129749</t>
+          <t>129851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151755</t>
+          <t>152523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47030</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56839</t>
+          <t>56645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155083</t>
+          <t>153429</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183876</t>
+          <t>182661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39951</t>
+          <t>40649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52829</t>
+          <t>52785</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>198709</t>
+          <t>200361</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232050</t>
+          <t>232935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>38836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>54503</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>32695</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44518</t>
+          <t>43180</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>71477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87861</t>
+          <t>88756</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126412</t>
+          <t>124479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150973</t>
+          <t>150291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202538</t>
+          <t>202300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232621</t>
+          <t>234011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>52013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,47 +6489,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>38752</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>28095</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>51496</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>12,98%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>27348</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>52124</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45756</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22446</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45836</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>306924</t>
+          <t>307201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>338976</t>
+          <t>337974</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>308572</t>
+          <t>307405</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>340039</t>
+          <t>339915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41497</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70429</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59814</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>92173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>108985</t>
+          <t>110027</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155404</t>
+          <t>154150</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49865</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>84086</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>94315</t>
+          <t>93781</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119141</t>
+          <t>119094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>167895</t>
+          <t>168668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>417477</t>
+          <t>417026</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>459168</t>
+          <t>459388</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>566623</t>
+          <t>568802</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>611264</t>
+          <t>616421</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>995118</t>
+          <t>998788</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1057656</t>
+          <t>1059863</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67792</t>
+          <t>67810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>35669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89519</t>
+          <t>88588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>40185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>56376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66673</t>
+          <t>66843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101192</t>
+          <t>101222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113869</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>42650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136476</t>
+          <t>135568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153679</t>
+          <t>153041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33093</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164472</t>
+          <t>164258</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182881</t>
+          <t>183794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73764</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91259</t>
+          <t>90927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246704</t>
+          <t>245181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270610</t>
+          <t>270120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>30455</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>51786</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104323</t>
+          <t>103638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122670</t>
+          <t>122495</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119256</t>
+          <t>120465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141114</t>
+          <t>141774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230229</t>
+          <t>230273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257613</t>
+          <t>259559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331222</t>
+          <t>332030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367209</t>
+          <t>365564</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331222</t>
+          <t>332030</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367209</t>
+          <t>365564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25834</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>34447</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>67858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>67832</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>105347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36332</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54490</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93046</t>
+          <t>90306</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>144469</t>
+          <t>140758</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>491916</t>
+          <t>491892</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>522488</t>
+          <t>523857</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>629765</t>
+          <t>627429</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>674597</t>
+          <t>674743</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1125910</t>
+          <t>1131322</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1186473</t>
+          <t>1188163</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101329</t>
+          <t>113620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96942</t>
+          <t>108555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>116578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58993</t>
+          <t>67685</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62129</t>
+          <t>71095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>160322</t>
+          <t>181306</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>153146</t>
+          <t>174307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164820</t>
+          <t>186134</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -11575,17 +11575,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84703</t>
+          <t>93787</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79462</t>
+          <t>87478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88986</t>
+          <t>98092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42024</t>
+          <t>49764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38201</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>126727</t>
+          <t>143551</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120599</t>
+          <t>136387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131753</t>
+          <t>148540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>87588</t>
+          <t>97787</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81204</t>
+          <t>91268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92381</t>
+          <t>102602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43773</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39578</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47388</t>
+          <t>51405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>131361</t>
+          <t>145215</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123146</t>
+          <t>137206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>151821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>26817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67147</t>
+          <t>53803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>182202</t>
+          <t>200546</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171070</t>
+          <t>187437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>191495</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>308900</t>
+          <t>111608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>275055</t>
+          <t>105607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322675</t>
+          <t>117034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>491102</t>
+          <t>312154</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>443758</t>
+          <t>298972</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>538636</t>
+          <t>324247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>30541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29851</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>25749</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>44850</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>36594</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>53884</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>76560</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>69261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74121</t>
+          <t>82925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>152779</t>
+          <t>164218</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143688</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160404</t>
+          <t>173081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>221480</t>
+          <t>240778</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211490</t>
+          <t>229449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>231849</t>
+          <t>251972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>295565</t>
+          <t>319298</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>295565</t>
+          <t>319298</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295565</t>
+          <t>319298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46335</t>
+          <t>50250</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>41253</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29666</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47691</t>
+          <t>51422</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>516</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>50823</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>41220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>61741</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47325</t>
+          <t>51339</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56318</t>
+          <t>62265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>237828</t>
+          <t>254887</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>225077</t>
+          <t>241836</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248776</t>
+          <t>267724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>239408</t>
+          <t>256466</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228002</t>
+          <t>242304</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>250378</t>
+          <t>268649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>47842</t>
+          <t>49734</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37795</t>
+          <t>40392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>62812</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>73789</t>
+          <t>78817</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>65897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97518</t>
+          <t>92575</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>121631</t>
+          <t>128552</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74251</t>
+          <t>111021</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>144806</t>
+          <t>145418</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>61929</t>
+          <t>65655</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51210</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>79452</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>100453</t>
+          <t>110413</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>97014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>130441</t>
+          <t>125023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>162382</t>
+          <t>176068</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>103775</t>
+          <t>157638</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192023</t>
+          <t>196447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>526103</t>
+          <t>583880</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>510728</t>
+          <t>564761</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>540836</t>
+          <t>597720</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>844297</t>
+          <t>695591</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>793715</t>
+          <t>675617</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>930011</t>
+          <t>713021</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1370400</t>
+          <t>1279471</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1323055</t>
+          <t>1253945</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1476548</t>
+          <t>1304362</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>635874</t>
+          <t>699270</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>635874</t>
+          <t>699270</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>635874</t>
+          <t>699270</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1654413</t>
+          <t>1584091</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1654413</t>
+          <t>1584091</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1654413</t>
+          <t>1584091</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
